--- a/DataDrivenTestingDemo/src/test/resources/Book1.xlsx
+++ b/DataDrivenTestingDemo/src/test/resources/Book1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestNG_Programs\DataDrivenTestingDemo\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC57520-30C0-462E-852A-81D8A369380B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5AC933-6A0F-4671-80F7-294A68D20320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1EF9C875-B9A8-461D-A55A-A3EDB786A7BF}"/>
   </bookViews>
@@ -42,16 +42,16 @@
     <t>password</t>
   </si>
   <si>
-    <t>hl@gmail.com</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>aadmin</t>
-  </si>
-  <si>
-    <t>hlm@gmail.com</t>
+    <t>anandkumar@gmail.com</t>
+  </si>
+  <si>
+    <t>Anandkumar@123</t>
+  </si>
+  <si>
+    <t>Anandkumar@gmail.com</t>
+  </si>
+  <si>
+    <t>anandkumar@123</t>
   </si>
 </sst>
 </file>
@@ -439,26 +439,28 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{85174FB1-46B4-49E6-92D2-A34FF3B81FB0}"/>
-    <hyperlink ref="B2" r:id="rId2" display="Anandkumar@123" xr:uid="{A5F251EC-77F1-42DC-9A91-3031AAC364C2}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{FF9EAE26-9BB8-4230-A086-6BFB96EDD2B6}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{094488A6-7718-4ABC-931A-E4C2DDE6BE3B}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{A5F251EC-77F1-42DC-9A91-3031AAC364C2}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{5F440089-181F-4245-AE00-C9972FFE24B2}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{AD440726-0555-4D83-A69A-528B5257370B}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{1C1D1E81-1CF4-4134-AAF5-4F482DE3BCE6}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{E2E349B4-989C-49A6-AB5B-574DE583A1AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
